--- a/content/sample-course/campaigns.xlsx
+++ b/content/sample-course/campaigns.xlsx
@@ -554,10 +554,10 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
